--- a/artfynd/A 46092-2023 artfynd.xlsx
+++ b/artfynd/A 46092-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46092-2023 artfynd.xlsx
+++ b/artfynd/A 46092-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1886737</v>
+        <v>88346</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>757975.6478527281</v>
+        <v>757881</v>
       </c>
       <c r="R2" t="n">
-        <v>7190358.804527947</v>
+        <v>7190358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,11 +760,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gammal asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2004386</v>
+        <v>1886737</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758000.132489071</v>
+        <v>757976</v>
       </c>
       <c r="R3" t="n">
-        <v>7190318.849697231</v>
+        <v>7190359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +845,11 @@
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +866,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>gammal sälg</t>
+          <t>gammal asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88346</v>
+        <v>1886738</v>
       </c>
       <c r="B4" t="n">
-        <v>77540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757880.7990897788</v>
+        <v>757751</v>
       </c>
       <c r="R4" t="n">
-        <v>7190357.529435101</v>
+        <v>7190518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,21 +952,11 @@
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,6 +969,14 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2 substratenheter # på två aspar</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1039,12 +997,7 @@
         <v>2057231</v>
       </c>
       <c r="B5" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757790.0834132928</v>
+        <v>757790</v>
       </c>
       <c r="R5" t="n">
-        <v>7190413.258482929</v>
+        <v>7190413</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,19 +1062,9 @@
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,15 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1886738</v>
+        <v>2004386</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757751.4809400712</v>
+        <v>758000</v>
       </c>
       <c r="R6" t="n">
-        <v>7190517.658287943</v>
+        <v>7190319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,21 +1169,11 @@
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1260,12 +1188,9 @@
           <t>Blandskog</t>
         </is>
       </c>
-      <c r="AN6" t="n">
-        <v>2</v>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2 substratenheter # på två aspar</t>
+          <t>gammal sälg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 46092-2023 artfynd.xlsx
+++ b/artfynd/A 46092-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88346</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1886737</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1886738</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2057231</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,8 +1230,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2004386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>